--- a/knowledge/business_data/DATA006_结构化业务数据_采购订单台账.xlsx
+++ b/knowledge/business_data/DATA006_结构化业务数据_采购订单台账.xlsx
@@ -13,11 +13,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,#00"/>
     <numFmt numFmtId="165" formatCode="¥#,##0;[Red](¥#,##0);-"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -651,7 +650,7 @@
         </is>
       </c>
       <c r="J3" s="30" t="n">
-        <v>45495</v>
+        <v>45463</v>
       </c>
       <c r="K3" s="30" t="n">
         <v>45537</v>
